--- a/eoe/Assets/Excels/HeroConfig.xlsx
+++ b/eoe/Assets/Excels/HeroConfig.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="16">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -67,19 +67,7 @@
     <t xml:space="preserve">gold</t>
   </si>
   <si>
-    <t xml:space="preserve">hero.101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hero.102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hero.103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hero.104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hero.105</t>
+    <t xml:space="preserve">Milo</t>
   </si>
 </sst>
 </file>
@@ -471,7 +459,7 @@
         <v>102</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="n">
         <v>2002</v>
@@ -518,7 +506,7 @@
         <v>103</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="n">
         <v>2003</v>
@@ -565,7 +553,7 @@
         <v>104</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="n">
         <v>2004</v>
@@ -612,7 +600,7 @@
         <v>105</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C6" s="1" t="n">
         <v>2005</v>

--- a/eoe/Assets/Excels/HeroConfig.xlsx
+++ b/eoe/Assets/Excels/HeroConfig.xlsx
@@ -344,7 +344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15.63" customWidth="1" style="2" min="1" max="1"/>
@@ -379,55 +379,50 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>ultimateId</t>
+          <t>health</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>health</t>
+          <t>attack</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
         <is>
-          <t>attack</t>
+          <t>attackRange</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>attackRange</t>
+          <t>attackSpeed</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>attackSpeed</t>
+          <t>critChance</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>critChance</t>
+          <t>critDamage</t>
         </is>
       </c>
       <c r="K1" s="2" t="inlineStr">
         <is>
-          <t>critDamage</t>
+          <t>lifesteal</t>
         </is>
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>lifesteal</t>
+          <t>skillCooldown</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>skillCooldown</t>
+          <t>expMultiplier</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>expMultiplier</t>
-        </is>
-      </c>
-      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>gold</t>
         </is>
@@ -435,7 +430,7 @@
     </row>
     <row r="2" ht="16.5" customHeight="1" s="3">
       <c r="A2" s="2" t="n">
-        <v>101</v>
+        <v>1001</v>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
@@ -443,56 +438,53 @@
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>2011</v>
+        <v>1101</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>2001</v>
+        <v>0</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>2001</v>
+        <v>20</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>5</v>
-      </c>
     </row>
     <row r="3" ht="16.5" customHeight="1" s="3">
-      <c r="O3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
     </row>
     <row r="4" ht="16.5" customHeight="1" s="3">
-      <c r="O4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1" s="3">
-      <c r="O5" s="2" t="n"/>
+      <c r="N5" s="2" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1" s="3">
-      <c r="O6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>

--- a/eoe/Assets/Excels/HeroConfig.xlsx
+++ b/eoe/Assets/Excels/HeroConfig.xlsx
@@ -1,63 +1,127 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="4"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="heros" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="heros" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefabName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attackId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skillId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attackRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attackSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critChance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">critDamage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lifesteal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">skillCooldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">expMultiplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milo Prefab</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
-    <font>
-      <name val="Arial"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="6">
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="1"/>
-      <family val="2"/>
-      <color rgb="FF000000"/>
-      <sz val="13"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -65,104 +129,57 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -339,103 +356,72 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:N6"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col width="15.63" customWidth="1" style="2" min="1" max="1"/>
-    <col width="18.45" customWidth="1" style="2" min="2" max="2"/>
-    <col width="15.63" customWidth="1" style="2" min="3" max="10"/>
-    <col width="17.82" customWidth="1" style="2" min="11" max="11"/>
-    <col width="17.39" customWidth="1" style="2" min="12" max="12"/>
-    <col width="16.43" customWidth="1" style="2" min="13" max="13"/>
-    <col width="15.63" customWidth="1" style="2" min="14" max="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="17.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="17.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="15.63"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" customHeight="1" s="3">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>prefabName</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>attackId</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>skillId</t>
-        </is>
-      </c>
-      <c r="E1" s="2" t="inlineStr">
-        <is>
-          <t>health</t>
-        </is>
-      </c>
-      <c r="F1" s="2" t="inlineStr">
-        <is>
-          <t>attack</t>
-        </is>
-      </c>
-      <c r="G1" s="2" t="inlineStr">
-        <is>
-          <t>attackRange</t>
-        </is>
-      </c>
-      <c r="H1" s="2" t="inlineStr">
-        <is>
-          <t>attackSpeed</t>
-        </is>
-      </c>
-      <c r="I1" s="2" t="inlineStr">
-        <is>
-          <t>critChance</t>
-        </is>
-      </c>
-      <c r="J1" s="2" t="inlineStr">
-        <is>
-          <t>critDamage</t>
-        </is>
-      </c>
-      <c r="K1" s="2" t="inlineStr">
-        <is>
-          <t>lifesteal</t>
-        </is>
-      </c>
-      <c r="L1" s="2" t="inlineStr">
-        <is>
-          <t>skillCooldown</t>
-        </is>
-      </c>
-      <c r="M1" s="2" t="inlineStr">
-        <is>
-          <t>expMultiplier</t>
-        </is>
-      </c>
-      <c r="N1" s="2" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="2" ht="16.5" customHeight="1" s="3">
+    <row r="2" s="3" customFormat="true" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
         <v>1001</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Milo</t>
-        </is>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>1101</v>
@@ -474,21 +460,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="16.5" customHeight="1" s="3">
-      <c r="N3" s="2" t="n"/>
-    </row>
-    <row r="4" ht="16.5" customHeight="1" s="3">
-      <c r="N4" s="2" t="n"/>
-    </row>
-    <row r="5" ht="16.5" customHeight="1" s="3">
-      <c r="N5" s="2" t="n"/>
-    </row>
-    <row r="6" ht="16.5" customHeight="1" s="3">
-      <c r="N6" s="2" t="n"/>
-    </row>
+    <row r="3" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="4" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="6" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>